--- a/data/example/Global_Scenarios.xlsx
+++ b/data/example/Global_Scenarios.xlsx
@@ -1,59 +1,252 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\example\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_0CE3D134B33217057B1CEA759839CF87F079A52F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2775" yWindow="2565" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>If a line has a value in this column, it is not read in (i.e., does not exist).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Readable name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Value specifier in database</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Description</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Details on database behavior</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Unit or valid values</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+  <si>
+    <t>Global - Scenarios and Probabilities</t>
+  </si>
+  <si>
+    <t>Format:</t>
+  </si>
+  <si>
+    <t>v0.1.0</t>
+  </si>
+  <si>
+    <t>Excl.</t>
+  </si>
+  <si>
+    <t>Database ID</t>
+  </si>
+  <si>
+    <t>Scenario ID</t>
+  </si>
+  <si>
+    <t>Relative Weight</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>excl</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>scenarioID</t>
+  </si>
+  <si>
+    <t>relativeWeight</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>ID within database</t>
+  </si>
+  <si>
+    <t>Scenario name</t>
+  </si>
+  <si>
+    <t>Relative weight of scenario (gets calculated relatively to all other scenarios)</t>
+  </si>
+  <si>
+    <t>Additional comments, manual adjustments, etc.</t>
+  </si>
+  <si>
+    <t>Filled automatically by database</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>[db-key]</t>
+  </si>
+  <si>
+    <t>[scenario]</t>
+  </si>
+  <si>
+    <t>[float]</t>
+  </si>
+  <si>
+    <t>[text]</t>
+  </si>
+  <si>
+    <t>ScenarioA</t>
+  </si>
+  <si>
+    <t>Example Scenario A</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>ScenarioB</t>
+  </si>
+  <si>
+    <t>Example Scenario B</t>
+  </si>
+  <si>
+    <t>ScenarioC</t>
+  </si>
+  <si>
+    <t>Example Scenario C</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Aptos"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
       <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="18"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Aptos"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -102,150 +295,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0" shapeId="0">
-      <text>
-        <t>If a line has a value in this column, it is not read in (i.e., does not exist).</t>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0" shapeId="0">
-      <text>
-        <t>Readable name</t>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0">
-      <text>
-        <t>Value specifier in database</t>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <t>Description</t>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0">
-      <text>
-        <t>Details on database behavior</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>Unit or valid values</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -532,235 +626,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor rgb="00008080"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <tabColor rgb="FF008080"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="5.5703125" customWidth="1" min="1" max="1"/>
-    <col width="19.7109375" customWidth="1" min="2" max="2"/>
-    <col width="41.7109375" customWidth="1" min="3" max="3"/>
-    <col width="15.7109375" customWidth="1" min="4" max="4"/>
-    <col width="100.7109375" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="100.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Global - Scenarios and Probabilities</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Format:</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Excl.</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Database ID</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Scenario ID</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Relative Weight</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>excl</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>scenarioID</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>relativeWeight</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>ID within database</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Scenario name</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Relative weight of scenario (gets calculated relatively to all other scenarios)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Additional comments, manual adjustments, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Filled automatically by database</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>[db-key]</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>[scenario]</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>[float]</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>[text]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>ScenarioA</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="n">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="13">
         <v>0.3</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Example Scenario A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>ScenarioB</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="n">
+      <c r="E8" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="13">
         <v>0.6</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Example Scenario B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>ScenarioC</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="n">
+      <c r="E9" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="13">
         <v>0.1</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Example Scenario C</t>
-        </is>
+      <c r="E10" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>